--- a/sample_data/output/excel/06_NICE_대출연체_시군구별.xlsx
+++ b/sample_data/output/excel/06_NICE_대출연체_시군구별.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,44 +496,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2382</v>
+        <v>378</v>
       </c>
       <c r="E2" t="n">
-        <v>19232.92857142857</v>
+        <v>33291.5</v>
       </c>
       <c r="F2" t="n">
-        <v>10069.28571428571</v>
+        <v>19891.5</v>
       </c>
       <c r="G2" t="n">
-        <v>43707046</v>
+        <v>10363421</v>
       </c>
       <c r="H2" t="n">
-        <v>22590439</v>
+        <v>4717257</v>
       </c>
       <c r="I2" t="n">
-        <v>5.177142857142857</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
-        <v>267</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>291.8571428571428</v>
+        <v>413.5</v>
       </c>
       <c r="L2" t="n">
-        <v>73643</v>
+        <v>7697</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001684922838299344</v>
+        <v>0.0007427084164582333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,91 +543,91 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1897</v>
+        <v>778</v>
       </c>
       <c r="E3" t="n">
-        <v>23328.58333333333</v>
+        <v>25502.25</v>
       </c>
       <c r="F3" t="n">
-        <v>12224.75</v>
+        <v>17073.75</v>
       </c>
       <c r="G3" t="n">
-        <v>45414578</v>
+        <v>18209716</v>
       </c>
       <c r="H3" t="n">
-        <v>22780822</v>
+        <v>11964492</v>
       </c>
       <c r="I3" t="n">
-        <v>5.453333333333333</v>
+        <v>4.045</v>
       </c>
       <c r="J3" t="n">
-        <v>189</v>
+        <v>62</v>
       </c>
       <c r="K3" t="n">
-        <v>283.8333333333333</v>
+        <v>251.75</v>
       </c>
       <c r="L3" t="n">
-        <v>48695</v>
+        <v>16461</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001072232797142803</v>
+        <v>0.0009039679696267641</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1777</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>14796.78571428571</v>
+        <v>20912</v>
       </c>
       <c r="F4" t="n">
-        <v>8517.928571428571</v>
+        <v>10699</v>
       </c>
       <c r="G4" t="n">
-        <v>31215922</v>
+        <v>669184</v>
       </c>
       <c r="H4" t="n">
-        <v>19108063</v>
+        <v>342368</v>
       </c>
       <c r="I4" t="n">
-        <v>5.484285714285714</v>
+        <v>2.47</v>
       </c>
       <c r="J4" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>281.5714285714286</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>23129</v>
+        <v>884</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007409359877308765</v>
+        <v>0.001321011859219587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -637,38 +637,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1203</v>
+        <v>229</v>
       </c>
       <c r="E5" t="n">
-        <v>12758.375</v>
+        <v>12072</v>
       </c>
       <c r="F5" t="n">
-        <v>5827.25</v>
+        <v>6030</v>
       </c>
       <c r="G5" t="n">
-        <v>31843628</v>
+        <v>2764488</v>
       </c>
       <c r="H5" t="n">
-        <v>14954522</v>
+        <v>1380870</v>
       </c>
       <c r="I5" t="n">
-        <v>3.88875</v>
+        <v>5.17</v>
       </c>
       <c r="J5" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="K5" t="n">
-        <v>162</v>
+        <v>289</v>
       </c>
       <c r="L5" t="n">
-        <v>10399</v>
+        <v>9248</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003265645484867491</v>
+        <v>0.00334528491351744</v>
       </c>
     </row>
     <row r="6">
@@ -679,49 +679,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1197</v>
+        <v>458</v>
       </c>
       <c r="E6" t="n">
-        <v>29983.8</v>
+        <v>13253</v>
       </c>
       <c r="F6" t="n">
-        <v>16018.9</v>
+        <v>5254</v>
       </c>
       <c r="G6" t="n">
-        <v>34385657</v>
+        <v>6069874</v>
       </c>
       <c r="H6" t="n">
-        <v>19472427</v>
+        <v>2406332</v>
       </c>
       <c r="I6" t="n">
-        <v>4.935</v>
+        <v>4.89</v>
       </c>
       <c r="J6" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="K6" t="n">
-        <v>169.6</v>
+        <v>168</v>
       </c>
       <c r="L6" t="n">
-        <v>19492</v>
+        <v>5208</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0005668642597115419</v>
+        <v>0.0008580079256999404</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -735,40 +735,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>847</v>
+        <v>651</v>
       </c>
       <c r="E7" t="n">
-        <v>24004.6</v>
+        <v>16155.5</v>
       </c>
       <c r="F7" t="n">
-        <v>12193.2</v>
+        <v>6049.5</v>
       </c>
       <c r="G7" t="n">
-        <v>22120186</v>
+        <v>7787785</v>
       </c>
       <c r="H7" t="n">
-        <v>12155336</v>
+        <v>3130272</v>
       </c>
       <c r="I7" t="n">
-        <v>6.31</v>
+        <v>6.635</v>
       </c>
       <c r="J7" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="K7" t="n">
-        <v>152.6</v>
+        <v>410</v>
       </c>
       <c r="L7" t="n">
-        <v>5537</v>
+        <v>18860</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002503143508829447</v>
+        <v>0.002421741226805825</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -782,40 +782,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>748</v>
+        <v>428</v>
       </c>
       <c r="E8" t="n">
-        <v>33443</v>
+        <v>43997</v>
       </c>
       <c r="F8" t="n">
-        <v>14550</v>
+        <v>15984</v>
       </c>
       <c r="G8" t="n">
-        <v>24965328</v>
+        <v>18830716</v>
       </c>
       <c r="H8" t="n">
-        <v>10151955</v>
+        <v>6841152</v>
       </c>
       <c r="I8" t="n">
-        <v>6.006666666666667</v>
+        <v>4.04</v>
       </c>
       <c r="J8" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="K8" t="n">
-        <v>189</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>13036</v>
+        <v>1221</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0005221641790566501</v>
+        <v>6.484086956651037e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -829,40 +829,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>937</v>
+        <v>499</v>
       </c>
       <c r="E9" t="n">
-        <v>10544.375</v>
+        <v>35192</v>
       </c>
       <c r="F9" t="n">
-        <v>4295.625</v>
+        <v>11730</v>
       </c>
       <c r="G9" t="n">
-        <v>8362404</v>
+        <v>17560808</v>
       </c>
       <c r="H9" t="n">
-        <v>3700917</v>
+        <v>5853270</v>
       </c>
       <c r="I9" t="n">
-        <v>4.52625</v>
+        <v>5.17</v>
       </c>
       <c r="J9" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>245.875</v>
+        <v>240</v>
       </c>
       <c r="L9" t="n">
-        <v>10007</v>
+        <v>1200</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001196665456488349</v>
+        <v>6.833398554326201e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -872,91 +872,91 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1514</v>
+        <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>29144.75</v>
+        <v>49773</v>
       </c>
       <c r="F10" t="n">
-        <v>12303</v>
+        <v>38025</v>
       </c>
       <c r="G10" t="n">
-        <v>41175192</v>
+        <v>1990920</v>
       </c>
       <c r="H10" t="n">
-        <v>17602183</v>
+        <v>1521000</v>
       </c>
       <c r="I10" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>34810</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0008454119655349756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3175</v>
+        <v>618</v>
       </c>
       <c r="E11" t="n">
-        <v>34468.05555555555</v>
+        <v>28187.75</v>
       </c>
       <c r="F11" t="n">
-        <v>17173.72222222222</v>
+        <v>17375.5</v>
       </c>
       <c r="G11" t="n">
-        <v>98196654</v>
+        <v>25542182</v>
       </c>
       <c r="H11" t="n">
-        <v>50976780</v>
+        <v>11741160</v>
       </c>
       <c r="I11" t="n">
-        <v>5.254444444444444</v>
+        <v>4.922499999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>324</v>
+        <v>53</v>
       </c>
       <c r="K11" t="n">
-        <v>261.9722222222222</v>
+        <v>229</v>
       </c>
       <c r="L11" t="n">
-        <v>90164</v>
+        <v>13683</v>
       </c>
       <c r="M11" t="n">
-        <v>0.000918198292173988</v>
+        <v>0.0005357020790158021</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -966,91 +966,91 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1441</v>
+        <v>541</v>
       </c>
       <c r="E12" t="n">
-        <v>30783.25</v>
+        <v>16048</v>
       </c>
       <c r="F12" t="n">
-        <v>18138.625</v>
+        <v>7546.5</v>
       </c>
       <c r="G12" t="n">
-        <v>45800090</v>
+        <v>9811552</v>
       </c>
       <c r="H12" t="n">
-        <v>25799208</v>
+        <v>3725268</v>
       </c>
       <c r="I12" t="n">
-        <v>4.24</v>
+        <v>6.324999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>114.375</v>
+        <v>136</v>
       </c>
       <c r="L12" t="n">
-        <v>11569</v>
+        <v>2203</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0002525977569039712</v>
+        <v>0.0002245312464327764</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1368</v>
+        <v>336</v>
       </c>
       <c r="E13" t="n">
-        <v>31175</v>
+        <v>36706</v>
       </c>
       <c r="F13" t="n">
-        <v>12949.4</v>
+        <v>16828.5</v>
       </c>
       <c r="G13" t="n">
-        <v>49179358</v>
+        <v>12893646</v>
       </c>
       <c r="H13" t="n">
-        <v>18993100</v>
+        <v>5424627</v>
       </c>
       <c r="I13" t="n">
-        <v>4.926</v>
+        <v>4.855</v>
       </c>
       <c r="J13" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K13" t="n">
-        <v>269.4</v>
+        <v>128</v>
       </c>
       <c r="L13" t="n">
-        <v>12272</v>
+        <v>5100</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0002495355876748127</v>
+        <v>0.0003955436654612668</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,91 +1060,91 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1195</v>
+        <v>821</v>
       </c>
       <c r="E14" t="n">
-        <v>15952.2</v>
+        <v>26100.5</v>
       </c>
       <c r="F14" t="n">
-        <v>10283.9</v>
+        <v>12677.25</v>
       </c>
       <c r="G14" t="n">
-        <v>17685914</v>
+        <v>26818672</v>
       </c>
       <c r="H14" t="n">
-        <v>11499800</v>
+        <v>10983487</v>
       </c>
       <c r="I14" t="n">
-        <v>5.636</v>
+        <v>5.27</v>
       </c>
       <c r="J14" t="n">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="K14" t="n">
-        <v>193.5</v>
+        <v>403.25</v>
       </c>
       <c r="L14" t="n">
-        <v>19901</v>
+        <v>18435</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001125245774688263</v>
+        <v>0.0006873942154928477</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2015</v>
+        <v>281</v>
       </c>
       <c r="E15" t="n">
-        <v>30615.33333333333</v>
+        <v>9364</v>
       </c>
       <c r="F15" t="n">
-        <v>17049.41666666667</v>
+        <v>6369</v>
       </c>
       <c r="G15" t="n">
-        <v>49852216</v>
+        <v>4765052</v>
       </c>
       <c r="H15" t="n">
-        <v>25260895</v>
+        <v>3329136</v>
       </c>
       <c r="I15" t="n">
-        <v>4.268333333333334</v>
+        <v>4.715</v>
       </c>
       <c r="J15" t="n">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>187.5833333333333</v>
+        <v>249</v>
       </c>
       <c r="L15" t="n">
-        <v>20404</v>
+        <v>4482</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0004092897294675928</v>
+        <v>0.0009405983397452955</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1154,91 +1154,91 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1491</v>
+        <v>403</v>
       </c>
       <c r="E16" t="n">
-        <v>25256.8</v>
+        <v>47138</v>
       </c>
       <c r="F16" t="n">
-        <v>12576.4</v>
+        <v>20570</v>
       </c>
       <c r="G16" t="n">
-        <v>39648031</v>
+        <v>18996614</v>
       </c>
       <c r="H16" t="n">
-        <v>17702865</v>
+        <v>8289710</v>
       </c>
       <c r="I16" t="n">
-        <v>5.64</v>
+        <v>4.84</v>
       </c>
       <c r="J16" t="n">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="K16" t="n">
-        <v>196.1</v>
+        <v>478</v>
       </c>
       <c r="L16" t="n">
-        <v>33842</v>
+        <v>28202</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0008535606724076664</v>
+        <v>0.00148458035732052</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2159</v>
+        <v>440</v>
       </c>
       <c r="E17" t="n">
-        <v>25407.35714285714</v>
+        <v>30043</v>
       </c>
       <c r="F17" t="n">
-        <v>14395.57142857143</v>
+        <v>10851</v>
       </c>
       <c r="G17" t="n">
-        <v>41492949</v>
+        <v>13218920</v>
       </c>
       <c r="H17" t="n">
-        <v>20662946</v>
+        <v>4774440</v>
       </c>
       <c r="I17" t="n">
-        <v>6.960357142857142</v>
+        <v>2.74</v>
       </c>
       <c r="J17" t="n">
-        <v>162</v>
+        <v>31</v>
       </c>
       <c r="K17" t="n">
-        <v>210.6071428571429</v>
+        <v>464</v>
       </c>
       <c r="L17" t="n">
-        <v>39263</v>
+        <v>14384</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0009462571580535285</v>
+        <v>0.001088137306224714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1248,96 +1248,96 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1887</v>
+        <v>133</v>
       </c>
       <c r="E18" t="n">
-        <v>22627</v>
+        <v>8365</v>
       </c>
       <c r="F18" t="n">
-        <v>13775.1</v>
+        <v>3253</v>
       </c>
       <c r="G18" t="n">
-        <v>38043168</v>
+        <v>1112545</v>
       </c>
       <c r="H18" t="n">
-        <v>22356458</v>
+        <v>432649</v>
       </c>
       <c r="I18" t="n">
-        <v>3.856</v>
+        <v>4.76</v>
       </c>
       <c r="J18" t="n">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>150.2</v>
+        <v>246</v>
       </c>
       <c r="L18" t="n">
-        <v>42343</v>
+        <v>3690</v>
       </c>
       <c r="M18" t="n">
-        <v>0.001113025077196515</v>
+        <v>0.003316719773132772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2644</v>
+        <v>273</v>
       </c>
       <c r="E19" t="n">
-        <v>23138.91666666667</v>
+        <v>23881</v>
       </c>
       <c r="F19" t="n">
-        <v>12826.80555555555</v>
+        <v>9506</v>
       </c>
       <c r="G19" t="n">
-        <v>68920825</v>
+        <v>6519513</v>
       </c>
       <c r="H19" t="n">
-        <v>38153234</v>
+        <v>2595138</v>
       </c>
       <c r="I19" t="n">
-        <v>5.706666666666667</v>
+        <v>4.84</v>
       </c>
       <c r="J19" t="n">
-        <v>205</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>328.4166666666667</v>
+        <v>497</v>
       </c>
       <c r="L19" t="n">
-        <v>60187</v>
+        <v>4473</v>
       </c>
       <c r="M19" t="n">
-        <v>0.000873277416513804</v>
+        <v>0.0006860941913912895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1346,45 +1346,45 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1445</v>
+        <v>289</v>
       </c>
       <c r="E20" t="n">
-        <v>22645.75</v>
+        <v>20173</v>
       </c>
       <c r="F20" t="n">
-        <v>12415.8125</v>
+        <v>7316</v>
       </c>
       <c r="G20" t="n">
-        <v>51045939</v>
+        <v>5829997</v>
       </c>
       <c r="H20" t="n">
-        <v>29733208</v>
+        <v>2114324</v>
       </c>
       <c r="I20" t="n">
-        <v>4.96375</v>
+        <v>4.23</v>
       </c>
       <c r="J20" t="n">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="K20" t="n">
-        <v>217.6875</v>
+        <v>279</v>
       </c>
       <c r="L20" t="n">
-        <v>38077</v>
+        <v>9765</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0007459359303783206</v>
+        <v>0.00167495798025282</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1393,45 +1393,45 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2688</v>
+        <v>591</v>
       </c>
       <c r="E21" t="n">
-        <v>27627.0625</v>
+        <v>32214.66666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>15455.0625</v>
+        <v>13231</v>
       </c>
       <c r="G21" t="n">
-        <v>82227935</v>
+        <v>24295675</v>
       </c>
       <c r="H21" t="n">
-        <v>49229620</v>
+        <v>9892848</v>
       </c>
       <c r="I21" t="n">
-        <v>4.15125</v>
+        <v>4.946666666666666</v>
       </c>
       <c r="J21" t="n">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>230.8125</v>
+        <v>156.6666666666667</v>
       </c>
       <c r="L21" t="n">
-        <v>71340</v>
+        <v>4319</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0008675883688432647</v>
+        <v>0.0001777682653394071</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1440,45 +1440,45 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2382</v>
+        <v>481</v>
       </c>
       <c r="E22" t="n">
-        <v>23657.1</v>
+        <v>392</v>
       </c>
       <c r="F22" t="n">
-        <v>11525.7</v>
+        <v>154</v>
       </c>
       <c r="G22" t="n">
-        <v>60351965</v>
+        <v>188552</v>
       </c>
       <c r="H22" t="n">
-        <v>29591218</v>
+        <v>74074</v>
       </c>
       <c r="I22" t="n">
-        <v>4.541</v>
+        <v>4.87</v>
       </c>
       <c r="J22" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="K22" t="n">
-        <v>349.5</v>
+        <v>233</v>
       </c>
       <c r="L22" t="n">
-        <v>39167</v>
+        <v>9786</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0006489763837846871</v>
+        <v>0.0519008019008019</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1487,45 +1487,45 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1360</v>
+        <v>1443</v>
       </c>
       <c r="E23" t="n">
-        <v>12482.5</v>
+        <v>24001.16666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>6388.666666666667</v>
+        <v>14029.16666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>27073272</v>
+        <v>31941378</v>
       </c>
       <c r="H23" t="n">
-        <v>15472385</v>
+        <v>21107783</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2925</v>
+        <v>5.633333333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="K23" t="n">
-        <v>248.4166666666667</v>
+        <v>87.33333333333333</v>
       </c>
       <c r="L23" t="n">
-        <v>13169</v>
+        <v>11672</v>
       </c>
       <c r="M23" t="n">
-        <v>0.000486420703046163</v>
+        <v>0.0003654194255488914</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1534,40 +1534,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1120</v>
+        <v>259</v>
       </c>
       <c r="E24" t="n">
-        <v>14016.5</v>
+        <v>7583</v>
       </c>
       <c r="F24" t="n">
-        <v>7564</v>
+        <v>3700</v>
       </c>
       <c r="G24" t="n">
-        <v>13605877</v>
+        <v>1963997</v>
       </c>
       <c r="H24" t="n">
-        <v>6810716</v>
+        <v>958300</v>
       </c>
       <c r="I24" t="n">
-        <v>4.140000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>320.25</v>
+        <v>349</v>
       </c>
       <c r="L24" t="n">
-        <v>32902</v>
+        <v>349</v>
       </c>
       <c r="M24" t="n">
-        <v>0.002418219714907021</v>
+        <v>0.0001776988457721677</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1577,91 +1577,91 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1388</v>
+        <v>326</v>
       </c>
       <c r="E25" t="n">
-        <v>19427.125</v>
+        <v>33239</v>
       </c>
       <c r="F25" t="n">
-        <v>11559.5</v>
+        <v>14945</v>
       </c>
       <c r="G25" t="n">
-        <v>27664442</v>
+        <v>10835914</v>
       </c>
       <c r="H25" t="n">
-        <v>17441885</v>
+        <v>4872070</v>
       </c>
       <c r="I25" t="n">
-        <v>4.31625</v>
+        <v>4.33</v>
       </c>
       <c r="J25" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="K25" t="n">
-        <v>285.375</v>
+        <v>345</v>
       </c>
       <c r="L25" t="n">
-        <v>30064</v>
+        <v>11730</v>
       </c>
       <c r="M25" t="n">
-        <v>0.001086737986618346</v>
+        <v>0.001082511359909279</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>654</v>
+        <v>490</v>
       </c>
       <c r="E26" t="n">
-        <v>23574.25</v>
+        <v>5018</v>
       </c>
       <c r="F26" t="n">
-        <v>11216.5</v>
+        <v>1517</v>
       </c>
       <c r="G26" t="n">
-        <v>11840391</v>
+        <v>2458820</v>
       </c>
       <c r="H26" t="n">
-        <v>5128303</v>
+        <v>743330</v>
       </c>
       <c r="I26" t="n">
-        <v>5.4425</v>
+        <v>2.84</v>
       </c>
       <c r="J26" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>250.25</v>
+        <v>39</v>
       </c>
       <c r="L26" t="n">
-        <v>16928</v>
+        <v>390</v>
       </c>
       <c r="M26" t="n">
-        <v>0.001429682516396629</v>
+        <v>0.0001586126678650735</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1671,44 +1671,44 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1651</v>
+        <v>753</v>
       </c>
       <c r="E27" t="n">
-        <v>17032</v>
+        <v>12057.5</v>
       </c>
       <c r="F27" t="n">
-        <v>8296.285714285714</v>
+        <v>4170</v>
       </c>
       <c r="G27" t="n">
-        <v>37005920</v>
+        <v>8512595</v>
       </c>
       <c r="H27" t="n">
-        <v>16178098</v>
+        <v>2944020</v>
       </c>
       <c r="I27" t="n">
-        <v>3.984285714285714</v>
+        <v>4.91</v>
       </c>
       <c r="J27" t="n">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="K27" t="n">
-        <v>226.1428571428571</v>
+        <v>84</v>
       </c>
       <c r="L27" t="n">
-        <v>37178</v>
+        <v>4830</v>
       </c>
       <c r="M27" t="n">
-        <v>0.001004650066800123</v>
+        <v>0.0005673945489007759</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1722,40 +1722,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2035</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
-        <v>31397.3</v>
+        <v>32345</v>
       </c>
       <c r="F28" t="n">
-        <v>18054</v>
+        <v>22515</v>
       </c>
       <c r="G28" t="n">
-        <v>55868333</v>
+        <v>2070080</v>
       </c>
       <c r="H28" t="n">
-        <v>31372082</v>
+        <v>1440960</v>
       </c>
       <c r="I28" t="n">
-        <v>4.07</v>
+        <v>7.41</v>
       </c>
       <c r="J28" t="n">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>169.1</v>
+        <v>124</v>
       </c>
       <c r="L28" t="n">
-        <v>24692</v>
+        <v>496</v>
       </c>
       <c r="M28" t="n">
-        <v>0.000441967724363639</v>
+        <v>0.0002396042665017777</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1769,40 +1769,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3440</v>
+        <v>213</v>
       </c>
       <c r="E29" t="n">
-        <v>34107.77777777778</v>
+        <v>14017</v>
       </c>
       <c r="F29" t="n">
-        <v>16290.80555555555</v>
+        <v>4982</v>
       </c>
       <c r="G29" t="n">
-        <v>114757419</v>
+        <v>2985621</v>
       </c>
       <c r="H29" t="n">
-        <v>58352355</v>
+        <v>1061166</v>
       </c>
       <c r="I29" t="n">
-        <v>5.622222222222223</v>
+        <v>3.45</v>
       </c>
       <c r="J29" t="n">
-        <v>329</v>
+        <v>27</v>
       </c>
       <c r="K29" t="n">
-        <v>174.7222222222223</v>
+        <v>171</v>
       </c>
       <c r="L29" t="n">
-        <v>75066</v>
+        <v>4617</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0006541276429369678</v>
+        <v>0.001546411952488276</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1812,91 +1812,91 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1531</v>
+        <v>753</v>
       </c>
       <c r="E30" t="n">
-        <v>20876.77777777778</v>
+        <v>21876</v>
       </c>
       <c r="F30" t="n">
-        <v>11609.13888888889</v>
+        <v>10955.5</v>
       </c>
       <c r="G30" t="n">
-        <v>27832212</v>
+        <v>16395265</v>
       </c>
       <c r="H30" t="n">
-        <v>14531135</v>
+        <v>8199435</v>
       </c>
       <c r="I30" t="n">
-        <v>5.370555555555556</v>
+        <v>6.11</v>
       </c>
       <c r="J30" t="n">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="L30" t="n">
-        <v>28336</v>
+        <v>5995</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0010181008969032</v>
+        <v>0.0003656543520339562</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1362</v>
+        <v>266</v>
       </c>
       <c r="E31" t="n">
-        <v>33813</v>
+        <v>38859</v>
       </c>
       <c r="F31" t="n">
-        <v>19971.33333333333</v>
+        <v>14683</v>
       </c>
       <c r="G31" t="n">
-        <v>45650196</v>
+        <v>10336494</v>
       </c>
       <c r="H31" t="n">
-        <v>27638293</v>
+        <v>3905678</v>
       </c>
       <c r="I31" t="n">
-        <v>5.579999999999999</v>
+        <v>3.51</v>
       </c>
       <c r="J31" t="n">
-        <v>148</v>
+        <v>35</v>
       </c>
       <c r="K31" t="n">
-        <v>315.3333333333333</v>
+        <v>266</v>
       </c>
       <c r="L31" t="n">
-        <v>44517</v>
+        <v>9310</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0009751765359342598</v>
+        <v>0.0009006922463264623</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>41130</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1906,91 +1906,91 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1395</v>
+        <v>157</v>
       </c>
       <c r="E32" t="n">
-        <v>23839.66666666667</v>
+        <v>14089</v>
       </c>
       <c r="F32" t="n">
-        <v>12846.5</v>
+        <v>6607</v>
       </c>
       <c r="G32" t="n">
-        <v>31787379</v>
+        <v>2211973</v>
       </c>
       <c r="H32" t="n">
-        <v>16285743</v>
+        <v>1037299</v>
       </c>
       <c r="I32" t="n">
-        <v>4.261944444444445</v>
+        <v>7.55</v>
       </c>
       <c r="J32" t="n">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>241</v>
+        <v>135</v>
       </c>
       <c r="L32" t="n">
-        <v>37890</v>
+        <v>675</v>
       </c>
       <c r="M32" t="n">
-        <v>0.001191982516079731</v>
+        <v>0.0003051574318493038</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1565</v>
+        <v>832</v>
       </c>
       <c r="E33" t="n">
-        <v>12069</v>
+        <v>18847</v>
       </c>
       <c r="F33" t="n">
-        <v>5614.125</v>
+        <v>8993.666666666666</v>
       </c>
       <c r="G33" t="n">
-        <v>17107543</v>
+        <v>13521421</v>
       </c>
       <c r="H33" t="n">
-        <v>7428810</v>
+        <v>6519664</v>
       </c>
       <c r="I33" t="n">
-        <v>4.6675</v>
+        <v>5.806666666666668</v>
       </c>
       <c r="J33" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="K33" t="n">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="L33" t="n">
-        <v>13832</v>
+        <v>12520</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0008085322363357496</v>
+        <v>0.0009259381835681323</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2000,91 +2000,91 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1205</v>
+        <v>97</v>
       </c>
       <c r="E34" t="n">
-        <v>18372.8</v>
+        <v>6951</v>
       </c>
       <c r="F34" t="n">
-        <v>11410.6</v>
+        <v>5467</v>
       </c>
       <c r="G34" t="n">
-        <v>21668375</v>
+        <v>674247</v>
       </c>
       <c r="H34" t="n">
-        <v>12548400</v>
+        <v>530299</v>
       </c>
       <c r="I34" t="n">
-        <v>5.711</v>
+        <v>6.96</v>
       </c>
       <c r="J34" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>194.4</v>
+        <v>116</v>
       </c>
       <c r="L34" t="n">
-        <v>15829</v>
+        <v>348</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0007305116327366496</v>
+        <v>0.0005161313287267129</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>974</v>
+        <v>553</v>
       </c>
       <c r="E35" t="n">
-        <v>29185.5</v>
+        <v>22849.5</v>
       </c>
       <c r="F35" t="n">
-        <v>10238.33333333333</v>
+        <v>16502</v>
       </c>
       <c r="G35" t="n">
-        <v>21421729</v>
+        <v>14380149</v>
       </c>
       <c r="H35" t="n">
-        <v>8067736</v>
+        <v>11177579</v>
       </c>
       <c r="I35" t="n">
-        <v>3.02</v>
+        <v>4.24</v>
       </c>
       <c r="J35" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K35" t="n">
-        <v>218.6666666666667</v>
+        <v>222</v>
       </c>
       <c r="L35" t="n">
-        <v>7554</v>
+        <v>9324</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0003526326002910409</v>
+        <v>0.0006483938379219854</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2094,91 +2094,91 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>720</v>
+        <v>445</v>
       </c>
       <c r="E36" t="n">
-        <v>23809.33333333333</v>
+        <v>45858</v>
       </c>
       <c r="F36" t="n">
-        <v>14307.66666666667</v>
+        <v>28430</v>
       </c>
       <c r="G36" t="n">
-        <v>19430464</v>
+        <v>20406810</v>
       </c>
       <c r="H36" t="n">
-        <v>10517024</v>
+        <v>12651350</v>
       </c>
       <c r="I36" t="n">
-        <v>6.833333333333333</v>
+        <v>4.91</v>
       </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="K36" t="n">
-        <v>72.66666666666667</v>
+        <v>305</v>
       </c>
       <c r="L36" t="n">
-        <v>2188</v>
+        <v>16470</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0001126066778436171</v>
+        <v>0.0008070835177080593</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1122</v>
+        <v>295</v>
       </c>
       <c r="E37" t="n">
-        <v>14784.64285714286</v>
+        <v>26121.5</v>
       </c>
       <c r="F37" t="n">
-        <v>7866.928571428572</v>
+        <v>20047</v>
       </c>
       <c r="G37" t="n">
-        <v>20613892</v>
+        <v>10323545</v>
       </c>
       <c r="H37" t="n">
-        <v>10666947</v>
+        <v>8200705</v>
       </c>
       <c r="I37" t="n">
-        <v>4.480714285714286</v>
+        <v>4.67</v>
       </c>
       <c r="J37" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="K37" t="n">
-        <v>280.3571428571428</v>
+        <v>142</v>
       </c>
       <c r="L37" t="n">
-        <v>30133</v>
+        <v>7186</v>
       </c>
       <c r="M37" t="n">
-        <v>0.001461781210457491</v>
+        <v>0.0006960787210207347</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2188,91 +2188,91 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>302</v>
+        <v>691</v>
       </c>
       <c r="E38" t="n">
-        <v>43008</v>
+        <v>21263</v>
       </c>
       <c r="F38" t="n">
-        <v>24606.5</v>
+        <v>14004</v>
       </c>
       <c r="G38" t="n">
-        <v>13625536</v>
+        <v>17152362</v>
       </c>
       <c r="H38" t="n">
-        <v>5958593</v>
+        <v>12017208</v>
       </c>
       <c r="I38" t="n">
-        <v>2.39</v>
+        <v>5.296666666666667</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="K38" t="n">
-        <v>396</v>
+        <v>240</v>
       </c>
       <c r="L38" t="n">
-        <v>6288</v>
+        <v>15897</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0004614864325337366</v>
+        <v>0.0009268111295692103</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3248</v>
+        <v>625</v>
       </c>
       <c r="E39" t="n">
-        <v>21131.86111111111</v>
+        <v>16278</v>
       </c>
       <c r="F39" t="n">
-        <v>12824.58333333333</v>
+        <v>9895</v>
       </c>
       <c r="G39" t="n">
-        <v>79753647</v>
+        <v>11285610</v>
       </c>
       <c r="H39" t="n">
-        <v>47580924</v>
+        <v>6920917</v>
       </c>
       <c r="I39" t="n">
-        <v>3.980555555555556</v>
+        <v>3.63</v>
       </c>
       <c r="J39" t="n">
-        <v>219</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>234.4444444444444</v>
+        <v>268</v>
       </c>
       <c r="L39" t="n">
-        <v>62465</v>
+        <v>28212</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0007832243709181098</v>
+        <v>0.00249982056796221</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>42110</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2282,96 +2282,96 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2021</v>
+        <v>529</v>
       </c>
       <c r="E40" t="n">
-        <v>29754</v>
+        <v>39483.5</v>
       </c>
       <c r="F40" t="n">
-        <v>16613.08333333333</v>
+        <v>21393.5</v>
       </c>
       <c r="G40" t="n">
-        <v>48543028</v>
+        <v>21171094</v>
       </c>
       <c r="H40" t="n">
-        <v>26245225</v>
+        <v>12070183</v>
       </c>
       <c r="I40" t="n">
-        <v>4.028333333333333</v>
+        <v>5.425</v>
       </c>
       <c r="J40" t="n">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="K40" t="n">
-        <v>249.4166666666667</v>
+        <v>285.5</v>
       </c>
       <c r="L40" t="n">
-        <v>38226</v>
+        <v>13892</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0007874663278112771</v>
+        <v>0.0006561777109864988</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1036</v>
+        <v>354</v>
       </c>
       <c r="E41" t="n">
-        <v>22559.5</v>
+        <v>44890</v>
       </c>
       <c r="F41" t="n">
-        <v>10565.6</v>
+        <v>14815</v>
       </c>
       <c r="G41" t="n">
-        <v>33232222</v>
+        <v>15891060</v>
       </c>
       <c r="H41" t="n">
-        <v>16691242</v>
+        <v>5244510</v>
       </c>
       <c r="I41" t="n">
-        <v>4.931</v>
+        <v>7.21</v>
       </c>
       <c r="J41" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>94.8</v>
+        <v>174</v>
       </c>
       <c r="L41" t="n">
-        <v>14853</v>
+        <v>2088</v>
       </c>
       <c r="M41" t="n">
-        <v>0.000446945738386076</v>
+        <v>0.0001313946332088608</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2380,45 +2380,45 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1794</v>
+        <v>454</v>
       </c>
       <c r="E42" t="n">
-        <v>22578.44444444445</v>
+        <v>3529</v>
       </c>
       <c r="F42" t="n">
-        <v>12873.94444444444</v>
+        <v>2311</v>
       </c>
       <c r="G42" t="n">
-        <v>36058519</v>
+        <v>1602166</v>
       </c>
       <c r="H42" t="n">
-        <v>21631952</v>
+        <v>1049194</v>
       </c>
       <c r="I42" t="n">
-        <v>5.608333333333333</v>
+        <v>6.69</v>
       </c>
       <c r="J42" t="n">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>195.8055555555556</v>
+        <v>366</v>
       </c>
       <c r="L42" t="n">
-        <v>20144</v>
+        <v>10980</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0005586474585936266</v>
+        <v>0.006853222450108166</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2427,45 +2427,45 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1984</v>
+        <v>819</v>
       </c>
       <c r="E43" t="n">
-        <v>31138.21428571429</v>
+        <v>25396.5</v>
       </c>
       <c r="F43" t="n">
-        <v>15812.42857142857</v>
+        <v>10286.5</v>
       </c>
       <c r="G43" t="n">
-        <v>63494209</v>
+        <v>20359703</v>
       </c>
       <c r="H43" t="n">
-        <v>30932223</v>
+        <v>8249226</v>
       </c>
       <c r="I43" t="n">
-        <v>4.402142857142857</v>
+        <v>7.445</v>
       </c>
       <c r="J43" t="n">
-        <v>160</v>
+        <v>47</v>
       </c>
       <c r="K43" t="n">
-        <v>201.6428571428571</v>
+        <v>273</v>
       </c>
       <c r="L43" t="n">
-        <v>26650</v>
+        <v>14020</v>
       </c>
       <c r="M43" t="n">
-        <v>0.000419723316814609</v>
+        <v>0.0006886151531778239</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2474,45 +2474,45 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1230</v>
+        <v>425</v>
       </c>
       <c r="E44" t="n">
-        <v>15984.4</v>
+        <v>12028.5</v>
       </c>
       <c r="F44" t="n">
-        <v>9008.6</v>
+        <v>5056</v>
       </c>
       <c r="G44" t="n">
-        <v>18521132</v>
+        <v>5112245</v>
       </c>
       <c r="H44" t="n">
-        <v>12634298</v>
+        <v>2334565</v>
       </c>
       <c r="I44" t="n">
-        <v>5.296</v>
+        <v>5.46</v>
       </c>
       <c r="J44" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>132.4</v>
+        <v>371</v>
       </c>
       <c r="L44" t="n">
-        <v>15796</v>
+        <v>7838</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0008528636370606289</v>
+        <v>0.00153318160612412</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2521,45 +2521,45 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1810</v>
+        <v>494</v>
       </c>
       <c r="E45" t="n">
-        <v>23514.1</v>
+        <v>41612</v>
       </c>
       <c r="F45" t="n">
-        <v>12934.3</v>
+        <v>16249</v>
       </c>
       <c r="G45" t="n">
-        <v>48475668</v>
+        <v>20556328</v>
       </c>
       <c r="H45" t="n">
-        <v>26677834</v>
+        <v>8027006</v>
       </c>
       <c r="I45" t="n">
-        <v>5.862</v>
+        <v>2.07</v>
       </c>
       <c r="J45" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>368.2</v>
+        <v>38</v>
       </c>
       <c r="L45" t="n">
-        <v>46990</v>
+        <v>114</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0009693522944335702</v>
+        <v>5.54573754612205e-06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2568,45 +2568,45 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1534</v>
+        <v>329</v>
       </c>
       <c r="E46" t="n">
-        <v>21541.5</v>
+        <v>28165</v>
       </c>
       <c r="F46" t="n">
-        <v>12515.3</v>
+        <v>21859</v>
       </c>
       <c r="G46" t="n">
-        <v>33344365</v>
+        <v>9266285</v>
       </c>
       <c r="H46" t="n">
-        <v>20502701</v>
+        <v>7191611</v>
       </c>
       <c r="I46" t="n">
-        <v>5.136</v>
+        <v>4.19</v>
       </c>
       <c r="J46" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>219.1</v>
+        <v>381</v>
       </c>
       <c r="L46" t="n">
-        <v>20656</v>
+        <v>381</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0006194749847537957</v>
+        <v>4.111680139343869e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2615,45 +2615,45 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>997</v>
+        <v>404</v>
       </c>
       <c r="E47" t="n">
-        <v>19100</v>
+        <v>31529</v>
       </c>
       <c r="F47" t="n">
-        <v>11932</v>
+        <v>15213</v>
       </c>
       <c r="G47" t="n">
-        <v>23215212</v>
+        <v>12737716</v>
       </c>
       <c r="H47" t="n">
-        <v>15862782</v>
+        <v>6146052</v>
       </c>
       <c r="I47" t="n">
-        <v>5.866000000000001</v>
+        <v>6.11</v>
       </c>
       <c r="J47" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="K47" t="n">
-        <v>184.6</v>
+        <v>347</v>
       </c>
       <c r="L47" t="n">
-        <v>17386</v>
+        <v>3123</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0007489055021336872</v>
+        <v>0.0002451773928701189</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2662,45 +2662,45 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1516</v>
+        <v>168</v>
       </c>
       <c r="E48" t="n">
-        <v>28339.63888888889</v>
+        <v>29371</v>
       </c>
       <c r="F48" t="n">
-        <v>15341.86111111111</v>
+        <v>12268</v>
       </c>
       <c r="G48" t="n">
-        <v>48698728</v>
+        <v>4934328</v>
       </c>
       <c r="H48" t="n">
-        <v>30029085</v>
+        <v>2061024</v>
       </c>
       <c r="I48" t="n">
-        <v>5.017222222222222</v>
+        <v>5.76</v>
       </c>
       <c r="J48" t="n">
-        <v>148</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>292.6666666666667</v>
+        <v>415</v>
       </c>
       <c r="L48" t="n">
-        <v>46588</v>
+        <v>830</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0009566574305595825</v>
+        <v>0.0001682093286056379</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>42110</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2709,45 +2709,45 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1559</v>
+        <v>208</v>
       </c>
       <c r="E49" t="n">
-        <v>34742.66666666666</v>
+        <v>40392</v>
       </c>
       <c r="F49" t="n">
-        <v>20426.75</v>
+        <v>16894</v>
       </c>
       <c r="G49" t="n">
-        <v>56956966</v>
+        <v>8401536</v>
       </c>
       <c r="H49" t="n">
-        <v>35650533</v>
+        <v>3513952</v>
       </c>
       <c r="I49" t="n">
-        <v>4.176666666666667</v>
+        <v>4.54</v>
       </c>
       <c r="J49" t="n">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="K49" t="n">
-        <v>239.5833333333333</v>
+        <v>114</v>
       </c>
       <c r="L49" t="n">
-        <v>41866</v>
+        <v>3306</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0007350461750367812</v>
+        <v>0.0003934994743818273</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2756,45 +2756,45 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2009</v>
+        <v>77</v>
       </c>
       <c r="E50" t="n">
-        <v>35078.25</v>
+        <v>36142</v>
       </c>
       <c r="F50" t="n">
-        <v>20394.16666666667</v>
+        <v>19422</v>
       </c>
       <c r="G50" t="n">
-        <v>66749649</v>
+        <v>2782934</v>
       </c>
       <c r="H50" t="n">
-        <v>37852242</v>
+        <v>1495494</v>
       </c>
       <c r="I50" t="n">
-        <v>5.638333333333333</v>
+        <v>4.81</v>
       </c>
       <c r="J50" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>109</v>
+        <v>375</v>
       </c>
       <c r="L50" t="n">
-        <v>21334</v>
+        <v>375</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0003196121675486264</v>
+        <v>0.0001347498718977885</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2803,45 +2803,45 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2307</v>
+        <v>220</v>
       </c>
       <c r="E51" t="n">
-        <v>24881</v>
+        <v>25345</v>
       </c>
       <c r="F51" t="n">
-        <v>12712.2</v>
+        <v>15425</v>
       </c>
       <c r="G51" t="n">
-        <v>58582900</v>
+        <v>5575900</v>
       </c>
       <c r="H51" t="n">
-        <v>31522855</v>
+        <v>3393500</v>
       </c>
       <c r="I51" t="n">
-        <v>5.854</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="K51" t="n">
-        <v>266.2</v>
+        <v>238</v>
       </c>
       <c r="L51" t="n">
-        <v>36268</v>
+        <v>6426</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0006190885053488304</v>
+        <v>0.001152459692605678</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2850,40 +2850,40 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2030</v>
+        <v>1046</v>
       </c>
       <c r="E52" t="n">
-        <v>21966.75</v>
+        <v>21686.33333333333</v>
       </c>
       <c r="F52" t="n">
-        <v>10574.08333333333</v>
+        <v>8463</v>
       </c>
       <c r="G52" t="n">
-        <v>51529198</v>
+        <v>26462036</v>
       </c>
       <c r="H52" t="n">
-        <v>22315368</v>
+        <v>9656710</v>
       </c>
       <c r="I52" t="n">
-        <v>5.139166666666667</v>
+        <v>2.31</v>
       </c>
       <c r="J52" t="n">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="K52" t="n">
-        <v>340.8333333333333</v>
+        <v>137.6666666666667</v>
       </c>
       <c r="L52" t="n">
-        <v>61801</v>
+        <v>23954</v>
       </c>
       <c r="M52" t="n">
-        <v>0.001199339450227811</v>
+        <v>0.000905221351826443</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2893,91 +2893,91 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1614</v>
+        <v>135</v>
       </c>
       <c r="E53" t="n">
-        <v>22394</v>
+        <v>9233</v>
       </c>
       <c r="F53" t="n">
-        <v>10796.16666666667</v>
+        <v>6668.5</v>
       </c>
       <c r="G53" t="n">
-        <v>37459672</v>
+        <v>982406</v>
       </c>
       <c r="H53" t="n">
-        <v>18027655</v>
+        <v>673012</v>
       </c>
       <c r="I53" t="n">
-        <v>6.448333333333333</v>
+        <v>3.985</v>
       </c>
       <c r="J53" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>266.8333333333333</v>
+        <v>32.5</v>
       </c>
       <c r="L53" t="n">
-        <v>27213</v>
+        <v>130</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0007264612461102169</v>
+        <v>0.0001323281820347188</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>44130</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2587</v>
+        <v>510</v>
       </c>
       <c r="E54" t="n">
-        <v>23587.22222222222</v>
+        <v>26987.5</v>
       </c>
       <c r="F54" t="n">
-        <v>11780.27777777778</v>
+        <v>16834.5</v>
       </c>
       <c r="G54" t="n">
-        <v>57113869</v>
+        <v>19852392</v>
       </c>
       <c r="H54" t="n">
-        <v>30581823</v>
+        <v>14366736</v>
       </c>
       <c r="I54" t="n">
-        <v>5.101111111111111</v>
+        <v>4.140000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="K54" t="n">
-        <v>212.9444444444445</v>
+        <v>355</v>
       </c>
       <c r="L54" t="n">
-        <v>34744</v>
+        <v>7315</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0006083286005365877</v>
+        <v>0.000368469451943121</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>44130</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2987,91 +2987,91 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1266</v>
+        <v>497</v>
       </c>
       <c r="E55" t="n">
-        <v>18050.8</v>
+        <v>15450</v>
       </c>
       <c r="F55" t="n">
-        <v>9016</v>
+        <v>8885</v>
       </c>
       <c r="G55" t="n">
-        <v>26375206</v>
+        <v>7678650</v>
       </c>
       <c r="H55" t="n">
-        <v>11324119</v>
+        <v>4415845</v>
       </c>
       <c r="I55" t="n">
-        <v>4.182</v>
+        <v>6.86</v>
       </c>
       <c r="J55" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>259.8</v>
+        <v>139</v>
       </c>
       <c r="L55" t="n">
-        <v>6532</v>
+        <v>1112</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0002476568334670069</v>
+        <v>0.0001448171228015341</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>44130</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1036</v>
+        <v>328</v>
       </c>
       <c r="E56" t="n">
-        <v>20031.6</v>
+        <v>30207</v>
       </c>
       <c r="F56" t="n">
-        <v>11669.6</v>
+        <v>21252</v>
       </c>
       <c r="G56" t="n">
-        <v>16234084</v>
+        <v>9907896</v>
       </c>
       <c r="H56" t="n">
-        <v>10743841</v>
+        <v>6970656</v>
       </c>
       <c r="I56" t="n">
-        <v>4.366</v>
+        <v>6.12</v>
       </c>
       <c r="J56" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>144.4</v>
+        <v>289</v>
       </c>
       <c r="L56" t="n">
-        <v>6620</v>
+        <v>2890</v>
       </c>
       <c r="M56" t="n">
-        <v>0.0004077840178725205</v>
+        <v>0.0002916865497982619</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>44130</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3081,602 +3081,85 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1896</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>26214.25</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="n">
-        <v>16648.625</v>
+        <v>30382</v>
       </c>
       <c r="G57" t="n">
-        <v>54697870</v>
+        <v>370424</v>
       </c>
       <c r="H57" t="n">
-        <v>37224129</v>
+        <v>243056</v>
       </c>
       <c r="I57" t="n">
-        <v>6.032500000000001</v>
+        <v>2.13</v>
       </c>
       <c r="J57" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>183.625</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>16791</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0003069772186741458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>45110</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1993</v>
+        <v>1230</v>
       </c>
       <c r="E58" t="n">
-        <v>21048.33333333333</v>
+        <v>20736.83333333333</v>
       </c>
       <c r="F58" t="n">
-        <v>12158.33333333333</v>
+        <v>10458.33333333333</v>
       </c>
       <c r="G58" t="n">
-        <v>46548311</v>
+        <v>20470519</v>
       </c>
       <c r="H58" t="n">
-        <v>28638904</v>
+        <v>10157520</v>
       </c>
       <c r="I58" t="n">
-        <v>4.948333333333333</v>
+        <v>4.899999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="K58" t="n">
-        <v>241.25</v>
+        <v>217.8333333333333</v>
       </c>
       <c r="L58" t="n">
-        <v>28159</v>
+        <v>20953</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0006049413908917125</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>45110</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E59" t="n">
-        <v>33446.25</v>
-      </c>
-      <c r="F59" t="n">
-        <v>17771.41666666667</v>
-      </c>
-      <c r="G59" t="n">
-        <v>63164670</v>
-      </c>
-      <c r="H59" t="n">
-        <v>35264585</v>
-      </c>
-      <c r="I59" t="n">
-        <v>4.476666666666667</v>
-      </c>
-      <c r="J59" t="n">
-        <v>174</v>
-      </c>
-      <c r="K59" t="n">
-        <v>272.8333333333333</v>
-      </c>
-      <c r="L59" t="n">
-        <v>64037</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.001013810410154917</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>45110</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1901</v>
-      </c>
-      <c r="E60" t="n">
-        <v>22510.58333333333</v>
-      </c>
-      <c r="F60" t="n">
-        <v>12205.58333333333</v>
-      </c>
-      <c r="G60" t="n">
-        <v>46042144</v>
-      </c>
-      <c r="H60" t="n">
-        <v>23155326</v>
-      </c>
-      <c r="I60" t="n">
-        <v>5.145833333333333</v>
-      </c>
-      <c r="J60" t="n">
-        <v>161</v>
-      </c>
-      <c r="K60" t="n">
-        <v>253.4166666666667</v>
-      </c>
-      <c r="L60" t="n">
-        <v>43975</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.0009551032202149405</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>45110</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1445</v>
-      </c>
-      <c r="E61" t="n">
-        <v>21703.7</v>
-      </c>
-      <c r="F61" t="n">
-        <v>11329.9</v>
-      </c>
-      <c r="G61" t="n">
-        <v>35044517</v>
-      </c>
-      <c r="H61" t="n">
-        <v>18380875</v>
-      </c>
-      <c r="I61" t="n">
-        <v>4.964</v>
-      </c>
-      <c r="J61" t="n">
-        <v>146</v>
-      </c>
-      <c r="K61" t="n">
-        <v>180.2</v>
-      </c>
-      <c r="L61" t="n">
-        <v>32095</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.0009158351362068993</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>46110</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1429</v>
-      </c>
-      <c r="E62" t="n">
-        <v>23273.8</v>
-      </c>
-      <c r="F62" t="n">
-        <v>11860</v>
-      </c>
-      <c r="G62" t="n">
-        <v>30771120</v>
-      </c>
-      <c r="H62" t="n">
-        <v>12470202</v>
-      </c>
-      <c r="I62" t="n">
-        <v>3.882</v>
-      </c>
-      <c r="J62" t="n">
-        <v>66</v>
-      </c>
-      <c r="K62" t="n">
-        <v>208.8</v>
-      </c>
-      <c r="L62" t="n">
-        <v>26216</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0.0008519676891838841</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>46110</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1145</v>
-      </c>
-      <c r="E63" t="n">
-        <v>31125.75</v>
-      </c>
-      <c r="F63" t="n">
-        <v>16583.5</v>
-      </c>
-      <c r="G63" t="n">
-        <v>35223131</v>
-      </c>
-      <c r="H63" t="n">
-        <v>19995367</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4.845000000000001</v>
-      </c>
-      <c r="J63" t="n">
-        <v>74</v>
-      </c>
-      <c r="K63" t="n">
-        <v>342.5</v>
-      </c>
-      <c r="L63" t="n">
-        <v>25960</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0.0007370156843808122</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>46110</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>779</v>
-      </c>
-      <c r="E64" t="n">
-        <v>20669.16666666667</v>
-      </c>
-      <c r="F64" t="n">
-        <v>13296.25</v>
-      </c>
-      <c r="G64" t="n">
-        <v>14734951</v>
-      </c>
-      <c r="H64" t="n">
-        <v>8161178</v>
-      </c>
-      <c r="I64" t="n">
-        <v>4.4225</v>
-      </c>
-      <c r="J64" t="n">
-        <v>84</v>
-      </c>
-      <c r="K64" t="n">
-        <v>154.0833333333333</v>
-      </c>
-      <c r="L64" t="n">
-        <v>20198</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0.001370754473496383</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>46110</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1864</v>
-      </c>
-      <c r="E65" t="n">
-        <v>18682.25</v>
-      </c>
-      <c r="F65" t="n">
-        <v>11761.25</v>
-      </c>
-      <c r="G65" t="n">
-        <v>53325229</v>
-      </c>
-      <c r="H65" t="n">
-        <v>37059027</v>
-      </c>
-      <c r="I65" t="n">
-        <v>4.940833333333333</v>
-      </c>
-      <c r="J65" t="n">
-        <v>141</v>
-      </c>
-      <c r="K65" t="n">
-        <v>301.0833333333333</v>
-      </c>
-      <c r="L65" t="n">
-        <v>46706</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0.0008758705940109512</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>47110</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2506</v>
-      </c>
-      <c r="E66" t="n">
-        <v>20421.16666666667</v>
-      </c>
-      <c r="F66" t="n">
-        <v>11078.41666666667</v>
-      </c>
-      <c r="G66" t="n">
-        <v>45665033</v>
-      </c>
-      <c r="H66" t="n">
-        <v>25274092</v>
-      </c>
-      <c r="I66" t="n">
-        <v>5.305000000000001</v>
-      </c>
-      <c r="J66" t="n">
-        <v>159</v>
-      </c>
-      <c r="K66" t="n">
-        <v>313.8333333333333</v>
-      </c>
-      <c r="L66" t="n">
-        <v>45758</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0.001002035846552438</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>47110</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1827</v>
-      </c>
-      <c r="E67" t="n">
-        <v>18077</v>
-      </c>
-      <c r="F67" t="n">
-        <v>12611.25</v>
-      </c>
-      <c r="G67" t="n">
-        <v>29832615</v>
-      </c>
-      <c r="H67" t="n">
-        <v>20304590</v>
-      </c>
-      <c r="I67" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="J67" t="n">
-        <v>149</v>
-      </c>
-      <c r="K67" t="n">
-        <v>299.375</v>
-      </c>
-      <c r="L67" t="n">
-        <v>48824</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0.001636598065573534</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>47110</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2531</v>
-      </c>
-      <c r="E68" t="n">
-        <v>26375.69047619048</v>
-      </c>
-      <c r="F68" t="n">
-        <v>15291.14285714286</v>
-      </c>
-      <c r="G68" t="n">
-        <v>65046991</v>
-      </c>
-      <c r="H68" t="n">
-        <v>39777323</v>
-      </c>
-      <c r="I68" t="n">
-        <v>5.306190476190477</v>
-      </c>
-      <c r="J68" t="n">
-        <v>269</v>
-      </c>
-      <c r="K68" t="n">
-        <v>195.5952380952381</v>
-      </c>
-      <c r="L68" t="n">
-        <v>84518</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0.001299337581964399</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>47110</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2239</v>
-      </c>
-      <c r="E69" t="n">
-        <v>23755.08333333333</v>
-      </c>
-      <c r="F69" t="n">
-        <v>11115.75</v>
-      </c>
-      <c r="G69" t="n">
-        <v>46209298</v>
-      </c>
-      <c r="H69" t="n">
-        <v>22014262</v>
-      </c>
-      <c r="I69" t="n">
-        <v>5.369166666666668</v>
-      </c>
-      <c r="J69" t="n">
-        <v>170</v>
-      </c>
-      <c r="K69" t="n">
-        <v>251</v>
-      </c>
-      <c r="L69" t="n">
-        <v>45706</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0.0009891082959104897</v>
+        <v>0.001023569553854497</v>
       </c>
     </row>
   </sheetData>
